--- a/data/PFI.MI.xlsx
+++ b/data/PFI.MI.xlsx
@@ -31054,6 +31054,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="G1335" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PFI.MI.xlsx
+++ b/data/PFI.MI.xlsx
@@ -31077,6 +31077,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PFI.MI.xlsx
+++ b/data/PFI.MI.xlsx
@@ -31100,6 +31100,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="G1337" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PFI.MI.xlsx
+++ b/data/PFI.MI.xlsx
@@ -30964,22 +30964,22 @@
     </row>
     <row r="1331">
       <c r="A1331" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1331" t="n">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.629999995231628</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="D1331" t="n">
-        <v>0.629999995231628</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="E1331" t="n">
-        <v>0.629999995231628</v>
+        <v>0.620000004768372</v>
       </c>
       <c r="F1331" t="n">
-        <v>0.629999995231628</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="G1331" t="s">
         <v>7</v>
@@ -30987,22 +30987,22 @@
     </row>
     <row r="1332">
       <c r="A1332" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1332" t="n">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.649999976158142</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="D1332" t="n">
-        <v>0.589999973773956</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="E1332" t="n">
-        <v>0.620000004768372</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="F1332" t="n">
-        <v>0.589999973773956</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="G1332" t="s">
         <v>7</v>
@@ -31010,19 +31010,19 @@
     </row>
     <row r="1333">
       <c r="A1333" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1333" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="C1333" t="n">
-        <v>0.589999973773956</v>
+        <v>0.649999976158142</v>
       </c>
       <c r="D1333" t="n">
         <v>0.589999973773956</v>
       </c>
       <c r="E1333" t="n">
-        <v>0.589999973773956</v>
+        <v>0.620000004768372</v>
       </c>
       <c r="F1333" t="n">
         <v>0.589999973773956</v>
@@ -31033,22 +31033,22 @@
     </row>
     <row r="1334">
       <c r="A1334" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1334" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.564999997615814</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="D1334" t="n">
-        <v>0.540000021457672</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="E1334" t="n">
-        <v>0.564999997615814</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="F1334" t="n">
-        <v>0.540000021457672</v>
+        <v>0.589999973773956</v>
       </c>
       <c r="G1334" t="s">
         <v>7</v>
@@ -31056,22 +31056,22 @@
     </row>
     <row r="1335">
       <c r="A1335" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1335" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.569999992847443</v>
+        <v>0.564999997615814</v>
       </c>
       <c r="D1335" t="n">
-        <v>0.560000002384186</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="E1335" t="n">
-        <v>0.560000002384186</v>
+        <v>0.564999997615814</v>
       </c>
       <c r="F1335" t="n">
-        <v>0.569999992847443</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="G1335" t="s">
         <v>7</v>
@@ -31079,19 +31079,19 @@
     </row>
     <row r="1336">
       <c r="A1336" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1336" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C1336" t="n">
         <v>0.569999992847443</v>
       </c>
       <c r="D1336" t="n">
-        <v>0.569999992847443</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="E1336" t="n">
-        <v>0.569999992847443</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="F1336" t="n">
         <v>0.569999992847443</v>
@@ -31102,7 +31102,7 @@
     </row>
     <row r="1337">
       <c r="A1337" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1337" t="n">
         <v>0</v>
@@ -31120,6 +31120,29 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1337" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="G1338" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PFI.MI.xlsx
+++ b/data/PFI.MI.xlsx
@@ -31215,6 +31215,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G1342" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
